--- a/output/pdf_financials_xlsx/NIR.H.xlsx
+++ b/output/pdf_financials_xlsx/NIR.H.xlsx
@@ -1110,13 +1110,13 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.336682</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.049006</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.011914</v>
       </c>
     </row>
     <row r="13">
@@ -2141,13 +2141,13 @@
         <v>31.593489</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.878152</v>
+        <v>1.54147</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.208362</v>
+        <v>-0.257368</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.282078</v>
+        <v>-0.293992</v>
       </c>
     </row>
     <row r="28">
@@ -2265,13 +2265,13 @@
         <v>31.593489</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.878152</v>
+        <v>1.54147</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.208362</v>
+        <v>-0.257368</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.282078</v>
+        <v>-0.293992</v>
       </c>
     </row>
     <row r="30">
@@ -2493,31 +2493,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.278543</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.540485</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.540485</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.978219</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.821226</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.658204</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.065127</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.502078</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.71975</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>11.226644</v>
@@ -2526,25 +2526,25 @@
         <v>7.756049</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>4.868869</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>5.470634</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>5.497578</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>7.480406</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.278997</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.017972</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.721897</v>
       </c>
     </row>
     <row r="35">
@@ -2615,31 +2615,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.278543</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.540485</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.540485</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.978219</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.821226</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.658204</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.065127</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.502078</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.71975</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.226644</v>
@@ -2648,25 +2648,25 @@
         <v>7.756049</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>4.868869</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>5.470634</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>5.497578</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>7.480406</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.278997</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>1.017972</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.721897</v>
       </c>
     </row>
     <row r="37">
@@ -3347,31 +3347,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.249861</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.498508</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.498508</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.437049</v>
+        <v>0.45883</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.539176</v>
+        <v>0.71795</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.482576</v>
+        <v>0.824372</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.96914</v>
+        <v>0.904013</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.371429</v>
+        <v>0.869351</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.469474</v>
+        <v>0.7497239999999999</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.074977</v>
@@ -3380,25 +3380,25 @@
         <v>1.710527</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>5.711315</v>
+        <v>0.842446</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>6.224574</v>
+        <v>0.7539400000000001</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>5.63948</v>
+        <v>0.141902</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>7.551407</v>
+        <v>0.07100099999999999</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.34219</v>
+        <v>0.063193</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.091236</v>
+        <v>0.073264</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.749664</v>
+        <v>0.027767</v>
       </c>
     </row>
     <row r="49">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -52572,7 +52572,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -56514,7 +56514,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -62004,7 +62004,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -64140,7 +64140,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -67594,7 +67594,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -69390,7 +69390,7 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
@@ -70866,7 +70866,7 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -75560,7 +75560,7 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E638" s="5" t="n">

--- a/output/pdf_financials_xlsx/NIR.H.xlsx
+++ b/output/pdf_financials_xlsx/NIR.H.xlsx
@@ -8016,7 +8016,7 @@
         <v>0</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>0</v>
+        <v>0.463706</v>
       </c>
       <c r="O123" s="3" t="n">
         <v>0</v>
@@ -8138,7 +8138,7 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>0.463706</v>
       </c>
       <c r="O125" s="3" t="n">
         <v>0</v>
@@ -36992,7 +36992,11 @@
           <t>Proceeds from long-term notes 7</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NIR.H.xlsx
+++ b/output/pdf_financials_xlsx/NIR.H.xlsx
@@ -7308,7 +7308,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.002227</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -7317,19 +7317,19 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.5379119999999999</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.040333</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.053939</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.092694</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.162557</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -44338,7 +44338,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -50284,7 +50288,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NIR.H.xlsx
+++ b/output/pdf_financials_xlsx/NIR.H.xlsx
@@ -1008,7 +1008,7 @@
         <v>0.562125</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.693902</v>
+        <v>0.596442</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1.928497</v>
@@ -1308,10 +1308,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-1.679638</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0.316469</v>
@@ -1338,13 +1336,13 @@
         <v>-8.960471</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>20.230965</v>
+        <v>19.990057</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-3.098589</v>
+        <v>-3.253278</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-3.760378</v>
+        <v>-3.781986</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-0.102085</v>
@@ -1381,10 +1379,10 @@
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3.2182</v>
+        <v>0.618</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.243354</v>
+        <v>1.430549</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.512324</v>
@@ -1399,13 +1397,13 @@
         <v>-0.244095</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>0.240908</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>0.154689</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>0.021608</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-0.001019</v>
@@ -1626,10 +1624,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-1.679638</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>0.316469</v>
@@ -1650,13 +1646,13 @@
         <v>-7.983646</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-10.232279</v>
+        <v>-8.626754999999999</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-9.204566</v>
+        <v>-5.144951</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>20.230965</v>
+        <v>-2.617571</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-3.098589</v>
@@ -1668,19 +1664,19 @@
         <v>-0.103104</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.267554</v>
+        <v>-0.409944</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>-2.988782</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>1.878152</v>
+        <v>-0.809644</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-0.208362</v>
+        <v>-0.260061</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>-0.282078</v>
+        <v>-0.291921</v>
       </c>
     </row>
     <row r="21">
@@ -1811,10 +1807,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-1.679638</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>0.316469</v>
@@ -2093,10 +2087,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-1.679638</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>0.316469</v>
@@ -2123,13 +2115,13 @@
         <v>-8.960471</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>20.230965</v>
+        <v>19.990057</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.098589</v>
+        <v>-3.253278</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.760378</v>
+        <v>-3.781986</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-0.102085</v>
@@ -2217,10 +2209,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-1.679638</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>0.316469</v>
@@ -2247,13 +2237,13 @@
         <v>-8.662482000000001</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>20.518683</v>
+        <v>20.277775</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.928177</v>
+        <v>-3.082866</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.504788</v>
+        <v>-3.526396</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>0.053557</v>
@@ -2280,10 +2270,8 @@
           <t>EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>-39.21902756944665</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>7.125494386631849</v>
@@ -2310,13 +2298,13 @@
         <v>-40.30319229861971</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>439.2913296480733</v>
+        <v>434.133649906013</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-47.95580275175643</v>
+        <v>-50.4891998694397</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-60.96456118342067</v>
+        <v>-61.34042478431504</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>0.9147844866680115</v>
@@ -2351,10 +2339,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>0</v>
@@ -2363,10 +2349,10 @@
         <v>0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>304.0693439105347</v>
+        <v>58.3912915719068</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-7.499033939388711</v>
+        <v>-44.08284023668639</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-10.37168280616287</v>
@@ -2381,13 +2367,13 @@
         <v>-2.72413135425582</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>1.205139134920926</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-4.754865707756915</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.5713400314014911</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0.9981877846892296</v>
@@ -2414,10 +2400,8 @@
           <t>Net Margin %</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="3" t="n">
+        <v>-39.21902756944665</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>7.125494386631849</v>
@@ -4754,22 +4738,22 @@
         <v>0</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.195567</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.20707</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.24004</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.243178</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.144275</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.07902000000000001</v>
       </c>
       <c r="K70" s="3" t="n">
         <v>0</v>
@@ -4778,10 +4762,10 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.09238</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.067789</v>
       </c>
       <c r="O70" s="3" t="n">
         <v>0</v>
@@ -4815,22 +4799,22 @@
         <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>1.199879</v>
+        <v>1.395446</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.570298</v>
+        <v>0.7773679999999999</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.22191</v>
+        <v>0.46195</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.424751</v>
+        <v>0.667929</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.540597</v>
+        <v>0.684872</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>24.338225</v>
+        <v>24.417245</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>0</v>
@@ -4839,10 +4823,10 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.09238</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.067789</v>
       </c>
       <c r="O71" s="3" t="n">
         <v>0</v>
@@ -5059,7 +5043,7 @@
         <v>0.044792</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.195567</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
         <v>2.438946</v>
@@ -5071,10 +5055,10 @@
         <v>0.469077</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.144275</v>
+        <v>0</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.07902000000000001</v>
+        <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
         <v>0</v>
@@ -5083,10 +5067,10 @@
         <v>0.174008</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.323758</v>
+        <v>0.231378</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.261974</v>
+        <v>0.194185</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>0.197026</v>
@@ -5370,22 +5354,22 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2.12227656787069</v>
+        <v>2.154159088671188</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2.18909324861093</v>
+        <v>2.212214076963428</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>2.851231430108502</v>
+        <v>2.875541621835341</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>3.555034017797237</v>
+        <v>3.582886210977918</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>-150.8068064597221</v>
+        <v>-151.4321261084769</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.5792359552999147</v>
+        <v>0.5810672953263146</v>
       </c>
       <c r="K80" s="1" t="inlineStr">
         <is>
@@ -5398,10 +5382,10 @@
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.06928880741957637</v>
+        <v>0.08782811544863399</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.001110391076831111</v>
+        <v>0.01479128906071046</v>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
@@ -6509,10 +6493,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-1.679638</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>0.316469</v>
@@ -6939,31 +6921,31 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>0.263505</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-0.205057</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-0.653772</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-0.635193</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-0.154384</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-1.234026</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-0.004203</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>0.6441170000000001</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>-0.184721</v>
       </c>
       <c r="K106" s="3" t="n">
         <v>-0.324383</v>
@@ -12388,7 +12370,11 @@
           <t>Lease liabilities 5</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -13436,7 +13422,11 @@
           <t>Lease liabilities 6</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -16142,7 +16132,11 @@
           <t>Current portion of license obligations (note 8)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -19172,7 +19166,11 @@
           <t>Current portion of license obligation (note 8)</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -22436,7 +22434,11 @@
           <t>Current portion of license obligation (note 9)</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -23726,7 +23728,11 @@
           <t>Current portion of license obligation (note 10)</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -25220,7 +25226,11 @@
           <t>Current portion of license obligation (note 11)</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -27256,7 +27266,11 @@
           <t>Current portion of license obligation (note 8) 195,567</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -36046,7 +36060,11 @@
           <t>Net income / (loss)</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -41006,7 +41024,11 @@
           <t>Change in non-cash operating working capital (note 16)</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -44034,7 +44056,11 @@
           <t>Change in non-cash operating working capital (note 16)</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -46294,7 +46320,11 @@
           <t>Change in non-cash operating working capital (note 17)</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -47242,7 +47272,11 @@
           <t>Change in non-cash operating working capital (note 18)</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -48592,7 +48626,11 @@
           <t>Change in non-cash operating working capital (note 18)</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -49544,7 +49582,11 @@
           <t>Change in non-cash operating working capital (note 15)</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -50398,7 +50440,11 @@
           <t>Change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E397" s="5" t="n">
         <v>0.263505</v>
       </c>
@@ -52488,7 +52534,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -55340,7 +55390,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E444" t="inlineStr">
         <is>
           <t>-</t>
@@ -57682,7 +57736,11 @@
           <t>Income tax (recovery) 9</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -58522,7 +58580,11 @@
           <t>Income tax (recovery) 9</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
           <t>-</t>
@@ -59266,7 +59328,11 @@
           <t>Income tax (recovery) 8</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>
@@ -59370,7 +59436,11 @@
           <t>Net (loss) from continuing operations</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E483" t="inlineStr">
         <is>
           <t>-</t>
@@ -61910,7 +61980,11 @@
           <t>LOSS FROM CONTINUING OPERATIONS</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -62542,7 +62616,11 @@
           <t>NET LOSS FROM CONTINUING OPERATIONS</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -64674,7 +64752,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr">
         <is>
           <t>-</t>
@@ -67712,7 +67794,11 @@
           <t>Income tax recovery (note 11)</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr"/>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E563" t="inlineStr">
         <is>
           <t>-</t>
@@ -69508,7 +69594,11 @@
           <t>Income tax recovery (note 12)</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E580" t="inlineStr">
         <is>
           <t>-</t>
@@ -71506,7 +71596,11 @@
           <t>Income tax recovery (note 13)</t>
         </is>
       </c>
-      <c r="D599" t="inlineStr"/>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E599" t="inlineStr">
         <is>
           <t>-</t>
@@ -71610,7 +71704,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
           <t>-</t>
@@ -72752,7 +72850,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D611" t="inlineStr"/>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E611" t="inlineStr">
         <is>
           <t>-</t>
@@ -77560,7 +77662,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D657" t="inlineStr"/>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E657" s="5" t="n">
         <v>-1.679638</v>
       </c>
